--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -68,6 +68,90 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>DENISSE MERARY</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>ROCIO</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -692,7 +776,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -722,6 +806,236 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920130</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920133</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920366</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920367</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920375</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920382</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920396</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920136</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920431</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920398</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -73,82 +73,40 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
+    <t>ZUÑIGA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>BRUNO</t>
+    <t>ROBLES</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>KAREN</t>
   </si>
   <si>
-    <t>DENISSE MERARY</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
+    <t>ARACELY</t>
   </si>
   <si>
     <t>ZURI SADAY</t>
   </si>
   <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
     <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>ROCIO</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
   </si>
   <si>
     <t>VALERIA</t>
@@ -552,19 +510,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -578,19 +536,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>51.52</v>
+        <v>69.7</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -646,7 +604,7 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -669,7 +627,7 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -728,19 +686,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -754,19 +712,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>51.52</v>
+        <v>69.7</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -776,7 +734,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -814,10 +772,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -831,16 +789,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920133</v>
+        <v>19330051920431</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -849,21 +807,21 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920366</v>
+        <v>19330051920367</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -872,21 +830,21 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920367</v>
+        <v>19330051920396</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -895,21 +853,21 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920375</v>
+        <v>19330051920398</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -918,121 +876,6 @@
         <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920382</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920396</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920136</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920431</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920398</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -76,9 +76,15 @@
     <t>ZUÑIGA</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -88,10 +94,13 @@
     <t>ROBLES</t>
   </si>
   <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>MORALES</t>
@@ -103,7 +112,13 @@
     <t>ARACELY</t>
   </si>
   <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
     <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
   </si>
   <si>
     <t>ELIZABETH</t>
@@ -601,16 +616,19 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>59.09</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -624,16 +642,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>45.45</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -698,7 +719,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -715,16 +736,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>69.7</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +755,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -772,10 +793,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -795,10 +816,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -807,27 +828,27 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920367</v>
+        <v>19330051920129</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -835,16 +856,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920396</v>
+        <v>19330051920367</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -858,16 +879,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920398</v>
+        <v>19330051920375</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -876,6 +897,52 @@
         <v>10</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920396</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920398</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
@@ -70,15 +70,15 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
     <t>ZUÑIGA</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>VERA</t>
   </si>
   <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -106,13 +106,13 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
     <t>KAREN</t>
   </si>
   <si>
     <t>ARACELY</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
   </si>
   <si>
     <t>ZURI SADAY</t>
@@ -787,13 +787,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920130</v>
+        <v>19330051920129</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>29</v>
@@ -805,18 +805,18 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920431</v>
+        <v>19330051920130</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>30</v>
@@ -828,12 +828,12 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920129</v>
+        <v>19330051920431</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -908,7 +908,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Mat</t>
   </si>
@@ -68,63 +68,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -616,16 +559,16 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>59.09</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H2">
         <v>7.3</v>
@@ -642,19 +585,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>45.45</v>
+        <v>69.7</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -710,16 +653,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>81.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -736,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>90.91</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -755,7 +698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -785,167 +728,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920129</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920130</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920431</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920367</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920375</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920396</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920398</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
